--- a/data/gravel/Marin Pine Mountain 2025.xlsx
+++ b/data/gravel/Marin Pine Mountain 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D239CA-1252-1B49-8A58-3D0BB6B71560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAA5456-8B6E-AB46-ADA7-F82A72DB635A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10840" yWindow="1120" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="1120" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -374,9 +374,6 @@
     <t>frame size</t>
   </si>
   <si>
-    <t>a1:f34</t>
-  </si>
-  <si>
     <t>threaded 73</t>
   </si>
   <si>
@@ -384,6 +381,9 @@
   </si>
   <si>
     <t>1 1/8" x 1 1/2"</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
   </si>
 </sst>
 </file>
@@ -795,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1429,7 +1429,7 @@
         <v>92</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1462,7 +1462,7 @@
         <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1514,7 +1514,7 @@
         <v>53</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Marin Pine Mountain 2025.xlsx
+++ b/data/gravel/Marin Pine Mountain 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EAA5456-8B6E-AB46-ADA7-F82A72DB635A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506A0A09-6002-494F-A6BF-DA45E7785DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="1120" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -338,9 +338,6 @@
     <t>suspension</t>
   </si>
   <si>
-    <t>Pine Mountain</t>
-  </si>
-  <si>
     <t>https://s3.us-east-1.amazonaws.com/craft-marinbikes/images/2020/bikes/hero/_bikeHero2649Wide/2023_Pine_Mountain_2_Color.jpg</t>
   </si>
   <si>
@@ -383,14 +380,26 @@
     <t>1 1/8" x 1 1/2"</t>
   </si>
   <si>
-    <t>a8:f34</t>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>Pine Mountain 2</t>
+  </si>
+  <si>
+    <t>RockShox 35 Gold RL, 120mm Travel</t>
+  </si>
+  <si>
+    <t>a8:f36</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -415,6 +424,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -436,13 +450,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -739,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -758,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -782,12 +797,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -795,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -803,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>74</v>
@@ -863,7 +878,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11">
         <v>66</v>
@@ -883,7 +898,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12">
         <v>95</v>
@@ -903,7 +918,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13">
         <v>75</v>
@@ -923,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14">
         <v>381</v>
@@ -943,7 +958,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15">
         <v>588.5</v>
@@ -978,7 +993,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -998,12 +1013,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18">
         <v>430</v>
@@ -1018,12 +1033,12 @@
         <v>430</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19">
         <v>1145</v>
@@ -1038,12 +1053,12 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20">
         <v>697.55</v>
@@ -1058,7 +1073,7 @@
         <v>818.91</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1078,7 +1093,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>88</v>
       </c>
@@ -1098,7 +1113,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1118,7 +1133,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1138,7 +1153,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -1158,407 +1173,431 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="C27">
+        <v>537</v>
+      </c>
+      <c r="D27">
+        <v>537</v>
+      </c>
+      <c r="E27">
+        <v>537</v>
+      </c>
+      <c r="F27">
+        <v>537</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28">
+        <v>120</v>
+      </c>
+      <c r="D28">
+        <v>120</v>
+      </c>
+      <c r="E28">
+        <v>120</v>
+      </c>
+      <c r="F28">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>26</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>26</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>700</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>700</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>700</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>700</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31">
-        <v>2.6</v>
-      </c>
-      <c r="D31">
-        <v>2.6</v>
-      </c>
-      <c r="E31">
-        <v>2.6</v>
-      </c>
-      <c r="F31">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32">
-        <v>2.6</v>
-      </c>
-      <c r="D32">
-        <v>2.6</v>
-      </c>
-      <c r="E32">
-        <v>2.6</v>
-      </c>
-      <c r="F32">
-        <v>2.6</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33">
+        <v>2.6</v>
+      </c>
+      <c r="D33">
+        <v>2.6</v>
+      </c>
+      <c r="E33">
+        <v>2.6</v>
+      </c>
+      <c r="F33">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <v>2.6</v>
+      </c>
+      <c r="D34">
+        <v>2.6</v>
+      </c>
+      <c r="E34">
+        <v>2.6</v>
+      </c>
+      <c r="F34">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>29</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="5">
-        <f>C35*2.54</f>
+      <c r="C35" s="5">
+        <f>C37*2.54</f>
         <v>160.02000000000001</v>
       </c>
-      <c r="D33" s="5">
-        <f t="shared" ref="D33:F34" si="0">D35*2.54</f>
+      <c r="D35" s="5">
+        <f t="shared" ref="D35:F36" si="0">D37*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E35" s="5">
         <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F35" s="5">
         <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="5">
-        <f>C36*2.54</f>
+      <c r="C36" s="5">
+        <f>C38*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D36" s="5">
         <f t="shared" si="0"/>
         <v>175.26</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E36" s="5">
         <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F36" s="5">
         <f t="shared" si="0"/>
         <v>190.5</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="C35">
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="C37">
         <v>63</v>
       </c>
-      <c r="D35">
+      <c r="D37">
         <v>66</v>
       </c>
-      <c r="E35">
+      <c r="E37">
         <v>69</v>
       </c>
-      <c r="F35">
+      <c r="F37">
         <v>72</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36">
-        <v>66</v>
-      </c>
-      <c r="D36">
-        <v>69</v>
-      </c>
-      <c r="E36">
-        <v>72</v>
-      </c>
-      <c r="F36">
-        <v>75</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>66</v>
+      </c>
+      <c r="D38">
         <v>69</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>89</v>
+      <c r="E38">
+        <v>72</v>
+      </c>
+      <c r="F38">
+        <v>75</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" ht="22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>99</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>70</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45">
-        <v>120</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="B47">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B48">
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49">
-        <v>148</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50">
-        <v>110</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>92</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>115</v>
+        <v>42</v>
+      </c>
+      <c r="B51" s="2">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>43</v>
+      </c>
+      <c r="B52">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>46</v>
-      </c>
-      <c r="B59">
-        <v>30.9</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>47</v>
-      </c>
-      <c r="B60" s="2"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="B61">
+        <v>30.9</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>49</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B62" s="2"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>54</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B72">
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1566,53 +1605,66 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B74" s="2"/>
+        <v>59</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B76" s="2"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>64</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B77" s="2"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B78">
-        <v>1499</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B78" s="2"/>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>67</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
+      </c>
+      <c r="B80">
+        <v>2399</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>90</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B83" t="s">
         <v>91</v>
       </c>
     </row>

--- a/data/gravel/Marin Pine Mountain 2025.xlsx
+++ b/data/gravel/Marin Pine Mountain 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506A0A09-6002-494F-A6BF-DA45E7785DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED71E2E-0746-9A44-A392-F8BE0E55C1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="1120" windowWidth="24840" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1428,6 +1428,9 @@
       <c r="A45" t="s">
         <v>36</v>
       </c>
+      <c r="B45">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
